--- a/test_doc/new_org/syllabus_5_social_studies.xlsx
+++ b/test_doc/new_org/syllabus_5_social_studies.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Maps and Globes</t>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Reading a map</t>
+          <t>Land and soil</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -461,22 +461,22 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>Directions and symbols</t>
+          <t>Forests and wildlife</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Our Country India</t>
+          <t>The Environment</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>States and capitals</t>
+          <t>Pollution</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -491,26 +491,26 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Physical features</t>
+          <t>Protecting nature</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Weather and Climate</t>
+          <t>Transport and Communication</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Seasons of India</t>
+          <t>Means of transport</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Weather around us</t>
+          <t>Staying in touch</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -531,12 +531,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Natural Resources</t>
+          <t>Maps and Globes</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Land and soil</t>
+          <t>Reading a map</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -544,14 +544,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Term 1</t>
+          <t>Term 2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Forests and wildlife</t>
+          <t>Directions and symbols</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -561,46 +561,46 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Transport and Communication</t>
+          <t>Our Country India</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Means of transport</t>
+          <t>States and capitals</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Term 1</t>
+          <t>Term 2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Staying in touch</t>
+          <t>Physical features</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Our Government</t>
+          <t>Weather and Climate</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Local bodies</t>
+          <t>Seasons of India</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -611,130 +611,10 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Why rules matter</t>
+          <t>Weather around us</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Great Personalities</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Freedom fighters</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Social reformers</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>The Environment</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Pollution</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Protecting nature</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Our Festivals and Culture</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Festivals of India</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Unity in diversity</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Disasters and Safety</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Floods and earthquakes</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Being prepared</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
         <v>3</v>
       </c>
     </row>
